--- a/course/spec/Course_Specification_ITCS355_merged.xlsx
+++ b/course/spec/Course_Specification_ITCS355_merged.xlsx
@@ -1663,7 +1663,7 @@
       </c>
       <c r="D13" s="17" t="inlineStr">
         <is>
-          <t>Budget TA time or automate with the scripts in instructor/.</t>
+          <t>Budget TA time or automate with the grading scripts in the private instructor repository.</t>
         </is>
       </c>
     </row>
@@ -3242,7 +3242,7 @@
     <row r="12">
       <c r="A12" s="17" t="inlineStr">
         <is>
-          <t>Session 5, LLM half — WRITTEN. Lab 5 Part B (Tasks 7 to 9) covers the evaluation gate, guardrails and token cost, backed by src/llmcost.py, scripts/llm_eval.py, a worked golden set under evals/ and tests; three slides in both decks; and the drill paper at instructor/drills/drill-05.md. STILL TO DO: a live managed-LLM-endpoint walkthrough for the room — the lab deliberately runs on recorded responses so it stays free, offline and identical for every student.</t>
+          <t>Session 5, LLM half — WRITTEN. Lab 5 Part B (Tasks 7 to 9) covers the evaluation gate, guardrails and token cost, backed by src/llmcost.py, scripts/llm_eval.py, a worked golden set under evals/ and tests; three slides in both decks; and the drill paper, which is in the private instructor repository and not here. STILL TO DO: a live managed-LLM-endpoint walkthrough for the room — the lab deliberately runs on recorded responses so it stays free, offline and identical for every student.</t>
         </is>
       </c>
       <c r="B12" s="17" t="n"/>
